--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-07-21T16:17:33.174Z</t>
+    <t>2026-07-21T16:45:23.362Z</t>
   </si>
   <si>
     <t>Power Confident Business Decisions | Dun &amp; Bradstreet</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-07-21T16:45:23.362Z</t>
+    <t>2026-07-21T17:34:47.654Z</t>
   </si>
   <si>
     <t>Power Confident Business Decisions | Dun &amp; Bradstreet</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,13 +52,31 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-07-21T17:34:47.654Z</t>
+    <t>2026-07-21T19:11:20.224Z</t>
   </si>
   <si>
     <t>Power Confident Business Decisions | Dun &amp; Bradstreet</t>
   </si>
   <si>
     <t>https://www.dnb.com/en-us/</t>
+  </si>
+  <si>
+    <t>fragments/schedule-a-strategy-session.report.json</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>fragments/schedule-a-strategy-session</t>
+  </si>
+  <si>
+    <t>form-fragment</t>
+  </si>
+  <si>
+    <t>2026-07-21T19:09:35.578Z</t>
+  </si>
+  <si>
+    <t>Schedule a Strategy Session</t>
   </si>
 </sst>
 </file>
@@ -447,13 +465,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="1" max="2" width="50" customWidth="1"/>
+    <col min="3" max="3" width="39" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="7" width="50" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
@@ -511,6 +528,32 @@
         <v>15</v>
       </c>
     </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
